--- a/シナリオ情報_製作者つき.xlsx
+++ b/シナリオ情報_製作者つき.xlsx
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>眞方／とんとん／yui</t>
+          <t>眞形／とんとん／yui</t>
         </is>
       </c>
     </row>

--- a/シナリオ情報_製作者つき.xlsx
+++ b/シナリオ情報_製作者つき.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="シナリオ情報" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'シナリオ情報'!$A$1:$F$791</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'シナリオ情報'!$A$1:$F$795</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F791"/>
+  <dimension ref="A1:F795"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -955,7 +955,11 @@
           <t>https://mdms.jp/scenarios/10720</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>緑</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1889,7 +1893,11 @@
           <t>https://mdms.jp/scenarios/2132</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>あそびばくろうさぎ合同会社</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2867,7 +2875,11 @@
           <t>https://mdms.jp/scenarios/11067</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>タンブルウィード レッドラム</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4149,7 +4161,11 @@
           <t>https://mdms.jp/scenarios/11284</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr"/>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>鯖井凌</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4717,7 +4733,11 @@
           <t>https://mdms.jp/scenarios/11267</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr"/>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>最東対地</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4807,7 +4827,11 @@
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>WorLd Holic</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4915,7 +4939,11 @@
           <t>https://mdms.jp/scenarios/91</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>白岩ぱんだ</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4953,7 +4981,11 @@
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>ドニパン</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7125,7 +7157,11 @@
           <t>https://mdms.jp/scenarios/11590</t>
         </is>
       </c>
-      <c r="F301" t="inlineStr"/>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>斐然</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -7213,7 +7249,11 @@
           <t>https://mdms.jp/scenarios/7118</t>
         </is>
       </c>
-      <c r="F305" t="inlineStr"/>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>ラピラボ</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -9249,7 +9289,11 @@
       <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr"/>
       <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr"/>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>御湯波ライト</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -9763,7 +9807,11 @@
           <t>https://mdms.jp/scenarios/10567</t>
         </is>
       </c>
-      <c r="F420" t="inlineStr"/>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>夏目美緒</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -10193,7 +10241,11 @@
           <t>https://mdms.jp/scenarios/3865</t>
         </is>
       </c>
-      <c r="F440" t="inlineStr"/>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>大原玲雄</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -12637,7 +12689,11 @@
           <t>https://mdms.jp/scenarios/11710</t>
         </is>
       </c>
-      <c r="F552" t="inlineStr"/>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>とんとん × クインズワルツ</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
@@ -13355,7 +13411,11 @@
           <t>https://mdms.jp/scenarios/10777</t>
         </is>
       </c>
-      <c r="F584" t="inlineStr"/>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>数羽</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
@@ -14191,7 +14251,11 @@
           <t>https://mdms.jp/scenarios/11282</t>
         </is>
       </c>
-      <c r="F621" t="inlineStr"/>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>小田ヨシキ（週末倶楽部）</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
@@ -16105,7 +16169,11 @@
           <t>https://mdms.jp/scenarios/9745</t>
         </is>
       </c>
-      <c r="F708" t="inlineStr"/>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>ぶるーそにあ</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="inlineStr">
@@ -16301,7 +16369,11 @@
           <t>https://mdms.jp/scenarios/6749</t>
         </is>
       </c>
-      <c r="F717" t="inlineStr"/>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>劉律舟</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
@@ -16459,7 +16531,11 @@
           <t>https://mdms.jp/scenarios/10265</t>
         </is>
       </c>
-      <c r="F724" t="inlineStr"/>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>タンブルウィード レッドラム</t>
+        </is>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="inlineStr">
@@ -17007,7 +17083,11 @@
         </is>
       </c>
       <c r="E748" t="inlineStr"/>
-      <c r="F748" t="inlineStr"/>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>Junya</t>
+        </is>
+      </c>
     </row>
     <row r="749">
       <c r="A749" t="inlineStr">
@@ -17041,7 +17121,11 @@
       </c>
       <c r="D750" t="inlineStr"/>
       <c r="E750" t="inlineStr"/>
-      <c r="F750" t="inlineStr"/>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>御湯波ライト・まめぽよ</t>
+        </is>
+      </c>
     </row>
     <row r="751">
       <c r="A751" t="inlineStr">
@@ -17061,7 +17145,11 @@
         </is>
       </c>
       <c r="E751" t="inlineStr"/>
-      <c r="F751" t="inlineStr"/>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>夏目美緒</t>
+        </is>
+      </c>
     </row>
     <row r="752">
       <c r="A752" t="inlineStr">
@@ -17077,7 +17165,11 @@
       </c>
       <c r="D752" t="inlineStr"/>
       <c r="E752" t="inlineStr"/>
-      <c r="F752" t="inlineStr"/>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>STUDIO ARTS</t>
+        </is>
+      </c>
     </row>
     <row r="753">
       <c r="A753" t="inlineStr">
@@ -17093,7 +17185,11 @@
       </c>
       <c r="D753" t="inlineStr"/>
       <c r="E753" t="inlineStr"/>
-      <c r="F753" t="inlineStr"/>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>newmerous</t>
+        </is>
+      </c>
     </row>
     <row r="754">
       <c r="A754" t="inlineStr">
@@ -17105,7 +17201,11 @@
       <c r="C754" t="inlineStr"/>
       <c r="D754" t="inlineStr"/>
       <c r="E754" t="inlineStr"/>
-      <c r="F754" t="inlineStr"/>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>ゆりあ</t>
+        </is>
+      </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
@@ -17225,7 +17325,11 @@
       </c>
       <c r="D759" t="inlineStr"/>
       <c r="E759" t="inlineStr"/>
-      <c r="F759" t="inlineStr"/>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>とんとん</t>
+        </is>
+      </c>
     </row>
     <row r="760">
       <c r="A760" t="inlineStr">
@@ -17241,7 +17345,11 @@
       </c>
       <c r="D760" t="inlineStr"/>
       <c r="E760" t="inlineStr"/>
-      <c r="F760" t="inlineStr"/>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>とんとん</t>
+        </is>
+      </c>
     </row>
     <row r="761">
       <c r="A761" t="inlineStr">
@@ -17269,7 +17377,11 @@
           <t>https://mdms.jp/scenarios/604</t>
         </is>
       </c>
-      <c r="F762" t="inlineStr"/>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>金の亡者（金儲け研究所）</t>
+        </is>
+      </c>
     </row>
     <row r="763">
       <c r="A763" t="inlineStr">
@@ -17313,7 +17425,11 @@
           <t>https://mdms.jp/scenarios/10959</t>
         </is>
       </c>
-      <c r="F764" t="inlineStr"/>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>すな</t>
+        </is>
+      </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
@@ -17383,7 +17499,11 @@
           <t>https://mdms.jp/scenarios/11815</t>
         </is>
       </c>
-      <c r="F767" t="inlineStr"/>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>伯川ろい</t>
+        </is>
+      </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
@@ -17429,7 +17549,11 @@
           <t>https://mdms.jp/scenarios/610</t>
         </is>
       </c>
-      <c r="F769" t="inlineStr"/>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>滝崎はじめ</t>
+        </is>
+      </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
@@ -17633,7 +17757,11 @@
       </c>
       <c r="D778" t="inlineStr"/>
       <c r="E778" t="inlineStr"/>
-      <c r="F778" t="inlineStr"/>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>白岩ぱんだ</t>
+        </is>
+      </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
@@ -17649,7 +17777,11 @@
       </c>
       <c r="D779" t="inlineStr"/>
       <c r="E779" t="inlineStr"/>
-      <c r="F779" t="inlineStr"/>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>花花世界</t>
+        </is>
+      </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
@@ -17665,7 +17797,11 @@
       </c>
       <c r="D780" t="inlineStr"/>
       <c r="E780" t="inlineStr"/>
-      <c r="F780" t="inlineStr"/>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>花花世界</t>
+        </is>
+      </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
@@ -17677,7 +17813,11 @@
       <c r="C781" t="inlineStr"/>
       <c r="D781" t="inlineStr"/>
       <c r="E781" t="inlineStr"/>
-      <c r="F781" t="inlineStr"/>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>幸田幸</t>
+        </is>
+      </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
@@ -17747,7 +17887,11 @@
           <t>https://mdms.jp/scenarios/7752</t>
         </is>
       </c>
-      <c r="F784" t="inlineStr"/>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>タンブルウィード レッドラム</t>
+        </is>
+      </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
@@ -17761,7 +17905,11 @@
       <c r="C785" t="inlineStr"/>
       <c r="D785" t="inlineStr"/>
       <c r="E785" t="inlineStr"/>
-      <c r="F785" t="inlineStr"/>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>タロサカ</t>
+        </is>
+      </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
@@ -17781,7 +17929,11 @@
           <t>https://mdms.jp/scenarios/7800</t>
         </is>
       </c>
-      <c r="F786" t="inlineStr"/>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>山口</t>
+        </is>
+      </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
@@ -17801,7 +17953,11 @@
           <t>https://mdms.jp/scenarios/11596</t>
         </is>
       </c>
-      <c r="F787" t="inlineStr"/>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>タコ教授</t>
+        </is>
+      </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
@@ -17873,7 +18029,11 @@
           <t>https://mdms.jp/scenarios/413</t>
         </is>
       </c>
-      <c r="F790" t="inlineStr"/>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>パーティ太郎</t>
+        </is>
+      </c>
     </row>
     <row r="791">
       <c r="A791" t="inlineStr">
@@ -17893,10 +18053,114 @@
           <t>https://mdms.jp/scenarios/604</t>
         </is>
       </c>
-      <c r="F791" t="inlineStr"/>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>金の亡者（金儲け研究所）</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>ワライバル</t>
+        </is>
+      </c>
+      <c r="B792" t="n">
+        <v>8</v>
+      </c>
+      <c r="C792" t="n">
+        <v>240</v>
+      </c>
+      <c r="D792" t="inlineStr"/>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>https://mdms.jp/scenarios/3264</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>2Uプロジェクト</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>ワライバル THE SECOND</t>
+        </is>
+      </c>
+      <c r="B793" t="n">
+        <v>8</v>
+      </c>
+      <c r="C793" t="n">
+        <v>240</v>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>ワライバル2</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>https://mdms.jp/scenarios/11122</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>2Uプロジェクト</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>真相は蒼炎に閉ざされた</t>
+        </is>
+      </c>
+      <c r="B794" t="n">
+        <v>6</v>
+      </c>
+      <c r="C794" t="n">
+        <v>120</v>
+      </c>
+      <c r="D794" t="inlineStr"/>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>https://mdms.jp/scenarios/11796</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>ねこまみれ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>このミステリーは王道すぎる</t>
+        </is>
+      </c>
+      <c r="B795" t="n">
+        <v>7</v>
+      </c>
+      <c r="C795" t="n">
+        <v>240</v>
+      </c>
+      <c r="D795" t="inlineStr"/>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>https://mdms.jp/scenarios/5046</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>JUNYA YAMAMOTO</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F791"/>
+  <autoFilter ref="A1:F795"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>